--- a/src/Ats.Web/wwwroot/templates/Mau_Nhap_Nhan_Su.xlsx
+++ b/src/Ats.Web/wwwroot/templates/Mau_Nhap_Nhan_Su.xlsx
@@ -81,7 +81,7 @@
     <x:t>Phải khớp chính xác tên chức vụ có trong hệ thống (Xem sheet 'Danh mục tham chiếu').</x:t>
   </x:si>
   <x:si>
-    <x:t>Senior Software Engineer (.NET &amp; React)</x:t>
+    <x:t>Senior Recruiter</x:t>
   </x:si>
   <x:si>
     <x:t>Vai trò (*)</x:t>
@@ -120,9 +120,6 @@
     <x:t>Phòng Nhân Sự</x:t>
   </x:si>
   <x:si>
-    <x:t>Senior Recruiter</x:t>
-  </x:si>
-  <x:si>
     <x:t>Recruiter</x:t>
   </x:si>
   <x:si>
@@ -172,6 +169,9 @@
   </x:si>
   <x:si>
     <x:t>Mô tả vai trò</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senior Software Engineer</x:t>
   </x:si>
   <x:si>
     <x:t>Admin</x:t>
@@ -917,7 +917,7 @@
     <x:col min="1" max="1" width="109.424911" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="103.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="36.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -1127,50 +1127,50 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
+      <x:c r="C4" s="18" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C4" s="18" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="C5" s="18" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C5" s="18" t="s">
+      <x:c r="D5" s="7" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="s">
+      <x:c r="E5" s="7" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="s">
+      <x:c r="F5" s="7" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="F5" s="7" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1191,7 +1191,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="36.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="16.282054" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="22.996339" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="41.424911" style="0" customWidth="1"/>
@@ -1199,19 +1199,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="26" customHeight="1">
       <x:c r="A1" s="19" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B1" s="19" t="s">
+      <x:c r="C1" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C1" s="19" t="s">
+      <x:c r="D1" s="19" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D1" s="19" t="s">
+      <x:c r="E1" s="19" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="E1" s="19" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1232,6 +1232,12 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
+      <x:c r="A3" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="C3" s="20" t="s">
         <x:v>55</x:v>
       </x:c>
@@ -1244,7 +1250,7 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="C4" s="20" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>58</x:v>
@@ -1266,7 +1272,7 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="C6" s="20" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>62</x:v>

--- a/src/Ats.Web/wwwroot/templates/Mau_Nhap_Nhan_Su.xlsx
+++ b/src/Ats.Web/wwwroot/templates/Mau_Nhap_Nhan_Su.xlsx
@@ -174,58 +174,58 @@
     <x:t>Senior Software Engineer</x:t>
   </x:si>
   <x:si>
+    <x:t>Candidate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ứng viên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Người nộp hồ sơ từ bên ngoài, không có tài khoản nội bộ (Nộp CV, theo dõi trạng thái hồ sơ, xác nhận lịch phỏng vấn và phản hồi offer)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nhân viên tuyển dụng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Người vận hành tuyển dụng hằng ngày (Sàng lọc CV, điều phối pipeline, đặt lịch phỏng vấn, soạn offer)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trưởng bộ phận</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Người cần người, sở hữu vị trí tuyển dụng (Tạo yêu cầu tuyển dụng, xem ứng viên của vị trí mình, quyết định tuyển)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Người phỏng vấn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nhân sự được mời tham gia một vòng phỏng vấn (Xem lịch, đọc CV, nộp phiếu đánh giá theo khung năng lực)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRManager</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trưởng phòng Nhân sự</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Chủ sở hữu toàn bộ hoạt động tuyển dụng (Giám sát tất cả vị trí, phân công recruiter, theo dõi ngân sách headcount và báo cáo)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approver</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Người duyệt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ban giám đốc hoặc cấp duyệt theo hạn mức (Phê duyệt yêu cầu tuyển dụng và offer vượt hạn mức lương)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Admin</x:t>
   </x:si>
   <x:si>
-    <x:t>Quản trị viên</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toàn quyền quản trị hệ thống</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRManager</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quản lý nhân sự</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quản lý tuyển dụng, duyệt yêu cầu và offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quản lý tuyển dụng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tạo yêu cầu tuyển dụng, tham gia phỏng vấn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Người phỏng vấn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tham gia phỏng vấn và đánh giá ứng viên</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Chuyên viên tuyển dụng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đăng tin, lọc hồ sơ, xếp lịch phỏng vấn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Approver</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Người phê duyệt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phê duyệt yêu cầu tuyển dụng và offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Candidate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ứng viên</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ứng viên nội bộ hoặc portal</x:t>
+    <x:t>Quản trị hệ thống</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Người vận hành ứng dụng (Quản lý tài khoản, vai trò, danh mục dùng chung, xem nhật ký hệ thống)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1193,8 +1193,8 @@
     <x:col min="1" max="1" width="26.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="23.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="16.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="41.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="122.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="26" customHeight="1">
@@ -1239,13 +1239,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C3" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="s">
+      <x:c r="E3" s="7" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1253,10 +1253,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -1264,15 +1264,15 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="E5" s="7" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="C6" s="20" t="s">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>62</x:v>
